--- a/data/trans_camb/IP19C01-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>5.102551738238814</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.872662851243283</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.4122713219263607</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>6.538696550456091</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.413030811138606</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>6.775642134188253</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-3.728756666988756</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.768565524867257</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.29341830222677</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.746721987707543</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-4.254342259882319</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.509996247336467</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>13.99483227318641</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>17.73011197149226</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.442796962170593</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>17.93150752517908</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9.028667791567162</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>15.14292901884429</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.07012950484818871</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.0944579236961525</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.005832855340137243</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.09251012394860965</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.03364862379709181</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.09448326648156044</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.04724211721841774</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.08925881973645354</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.1352049798254933</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.08976110359735727</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.05612931893967558</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.03499877131651172</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.2078995187313847</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.2611717821316647</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.1356090378626367</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.2752806933022907</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.131913247073465</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2190472270362409</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-0.5238074100641033</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6.289394751032152</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.770390371583508</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>7.721882396656299</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.5702063654038692</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6.999463854045851</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-9.771723741961759</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.8801096981672</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.982720280697611</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.969017808883742</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-6.571141410926586</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.6210460074582442</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>9.129328886218675</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>15.85841159420341</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>11.13352043742119</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>16.28760550493487</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>7.241547916638703</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>13.56423769280125</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.006655610654333362</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.07991441493573971</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.02328065892144298</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.1015428648921401</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.007365075863229842</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.09040864047610124</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.1195990728546489</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.03362311931136121</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.09719723180451841</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.03786978308603321</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.08269313631732474</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.007873185008284366</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.1253273088620594</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.2166450940146157</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.1592911448718718</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.2307336871827787</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.09714327861746475</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1852489364356239</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-7.029902191911841</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7.581092705925707</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.61653737765051</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>12.90029437793182</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.8185860924007193</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>10.167429591238</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-18.24519692597831</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.588100051142737</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.165379154518425</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>2.200438296387137</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-9.201034464942566</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>3.347363911950192</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>4.004482826409915</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>16.5889923158241</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>16.60505250684618</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>22.2684812588852</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>7.783397386702178</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>17.47310738525657</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.09094732146337643</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.09807818893451399</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.07812678564120594</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.1794448190772545</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.01096239872317007</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.1361608976791005</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.2275605613920335</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.015039898026843</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.06690552421854878</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.03165555575048563</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.1180917278294618</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.04346615263237991</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.05414544810304388</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.237647669767178</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.25600573328078</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.3496335646716442</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1100277644315523</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2501789578639026</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>1.076100123890911</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4.2131589065596</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.143458051586865</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>7.741905896702351</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.141973069108582</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>5.85641738247581</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-13.52198024588257</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-8.072241528732917</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-15.30147674134625</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-5.70155214557928</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-9.047096865885283</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-3.809164278933878</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>16.30741178391692</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>18.37695286291119</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>19.3838977656553</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>23.39802279296267</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>12.46907994934473</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>15.87892396925629</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.01431634751472272</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.05605151946546103</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.016827680477687</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.1139336231331186</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.01590680805151407</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.08157539761013009</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.1615773922278864</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.09666670663182632</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.202550544353596</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.07346115223615307</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.1160196835892484</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.04816534801722029</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.243877412436464</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.2808808244498059</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.3328623564361072</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.4072258034312072</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.2053865578973964</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.2484762578287928</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.0230184482248097</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>6.941581339757564</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1.488559353113883</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>8.965635714395393</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.6980767515017861</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>7.982673774874415</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-5.044116530854134</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2.432515879676882</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.667724936612433</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>3.742128668154106</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.925352332251252</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>4.409684542573443</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>5.382890468956634</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>12.40846985671266</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>6.724308893259695</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>14.27212407707338</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>4.504334745513038</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>11.68609392962452</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.0003026619197503935</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.09127254425995965</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.0205851066642248</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.1239846883547765</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.00940458047439887</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.1075436157344767</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.06360027359668712</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.0301376252918775</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.04995970766860332</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.050325023606797</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.03887028224445047</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.05770650614636106</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.07165316979664156</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.1696214019287816</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.09789687053708848</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.2076694926457104</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.0619087938272723</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.1629715624253463</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
